--- a/AAII_Financials/Yearly/CYN_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/CYN_YR_FIN.xlsx
@@ -1950,10 +1950,10 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>33700</v>
+        <v>33800</v>
       </c>
       <c r="E42" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F42" s="3">
         <v>4600</v>
@@ -2076,10 +2076,10 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="E45" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="F45" s="3">
         <v>200</v>
